--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_COTO CÓRDOBA CB.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_COTO CÓRDOBA CB.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7999</v>
+        <v>7.7206</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7646</v>
+        <v>6.9125</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0353</v>
+        <v>0.8081</v>
       </c>
       <c r="G2" t="n">
-        <v>3.646199999999999</v>
+        <v>3.6265</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5562</v>
+        <v>2.5691</v>
       </c>
       <c r="I2" t="n">
-        <v>1.09</v>
+        <v>1.0574</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0563</v>
+        <v>6.1498</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8708</v>
+        <v>4.9571</v>
       </c>
       <c r="L2" t="n">
-        <v>1.1854</v>
+        <v>1.1926</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.4101</v>
+        <v>-2.5233</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.3146</v>
+        <v>-2.3881</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.09540000000000004</v>
+        <v>-0.1352</v>
       </c>
       <c r="P2" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R2" t="n">
-        <v>4.7115</v>
+        <v>4.6564</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3231</v>
+        <v>2.3083</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2728</v>
+        <v>2.2852</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0504</v>
+        <v>0.02300000000000002</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8324</v>
+        <v>-0.846</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4841000000000001</v>
+        <v>0.5018999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3165</v>
+        <v>-1.3479</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4582</v>
+        <v>4.4206</v>
       </c>
       <c r="E3" t="n">
-        <v>5.968</v>
+        <v>6.0202</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5097</v>
+        <v>-1.5996</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1185</v>
+        <v>-0.1381</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4079</v>
+        <v>1.4225</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5264</v>
+        <v>-1.5606</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4168</v>
+        <v>2.4544</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5475</v>
+        <v>1.5798</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8693</v>
+        <v>0.8746</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5353</v>
+        <v>-2.5925</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1397</v>
+        <v>-0.1572</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.3957</v>
+        <v>-2.4352</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2049000000000001</v>
+        <v>0.2023999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1299</v>
+        <v>4.1052</v>
       </c>
       <c r="T3" t="n">
-        <v>4.2962</v>
+        <v>4.2787</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1663</v>
+        <v>-0.1735</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4842</v>
+        <v>0.5018</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.084</v>
+        <v>4.110799999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>6.195200000000001</v>
+        <v>6.4325</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1112</v>
+        <v>-2.3218</v>
       </c>
       <c r="G4" t="n">
-        <v>7.9438</v>
+        <v>7.9713</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6915000000000002</v>
+        <v>0.7106999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2522</v>
+        <v>7.2606</v>
       </c>
       <c r="J4" t="n">
-        <v>9.879999999999999</v>
+        <v>10.0202</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9504</v>
+        <v>3.0396</v>
       </c>
       <c r="L4" t="n">
-        <v>6.929600000000001</v>
+        <v>6.9806</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9363</v>
+        <v>-2.0489</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2589</v>
+        <v>-2.329</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3226</v>
+        <v>0.2801</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2049000000000003</v>
+        <v>-0.2024000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="R4" t="n">
-        <v>3.8921</v>
+        <v>3.8466</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.3385</v>
+        <v>-2.3102</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3588</v>
+        <v>-1.3239</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9797</v>
+        <v>-0.9862</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.3165</v>
+        <v>-1.3479</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.0874</v>
+        <v>-3.1332</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1179</v>
+        <v>2.1707</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8475</v>
+        <v>3.104</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7296</v>
+        <v>-0.9333</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0394</v>
+        <v>2.1032</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0109999999999999</v>
+        <v>-0.000600000000000156</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0505</v>
+        <v>2.1038</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5938</v>
+        <v>4.7674</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0527</v>
+        <v>2.1309</v>
       </c>
       <c r="L5" t="n">
-        <v>2.541</v>
+        <v>2.6365</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5543</v>
+        <v>-2.6642</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0637</v>
+        <v>-2.1314</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4906</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6145</v>
+        <v>-0.6073999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.0969</v>
+        <v>-4.0491</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4824</v>
+        <v>3.4417</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2833</v>
+        <v>1.2698</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9279999999999999</v>
+        <v>0.9444</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3552000000000001</v>
+        <v>0.3253999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5902999999999998</v>
+        <v>-0.5951000000000002</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.013</v>
+        <v>-2.0362</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0928</v>
+        <v>2.0438</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0298</v>
+        <v>2.2117</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06290000000000007</v>
+        <v>-0.1679</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.355</v>
+        <v>-0.3524</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5051</v>
+        <v>-1.5025</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1502</v>
+        <v>1.15</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1862</v>
+        <v>2.2989</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3614000000000001</v>
+        <v>-0.2997</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5476</v>
+        <v>2.5985</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5411</v>
+        <v>-2.6514</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1437</v>
+        <v>-1.2028</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3974</v>
+        <v>-1.4485</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R6" t="n">
-        <v>4.3018</v>
+        <v>4.2515</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3992</v>
+        <v>2.3718</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4938</v>
+        <v>1.5084</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9055</v>
+        <v>0.8633</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.6033</v>
+        <v>-2.6313</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5723</v>
+        <v>-1.4291</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1435</v>
+        <v>0.1431</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4288</v>
+        <v>-1.5722</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9012000000000002</v>
+        <v>0.9467999999999996</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0789</v>
+        <v>-2.0569</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9802</v>
+        <v>3.0037</v>
       </c>
       <c r="J7" t="n">
-        <v>3.748499999999999</v>
+        <v>3.8763</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6045</v>
+        <v>-1.5449</v>
       </c>
       <c r="L7" t="n">
-        <v>5.353</v>
+        <v>5.4212</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8472</v>
+        <v>-2.9295</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4744</v>
+        <v>-0.512</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.3728</v>
+        <v>-2.4175</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.7115</v>
+        <v>-4.6564</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.3746</v>
+        <v>-7.2882</v>
       </c>
       <c r="R7" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.259</v>
+        <v>-0.2575999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1951</v>
+        <v>-0.1733</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0639</v>
+        <v>-0.0843</v>
       </c>
       <c r="V7" t="n">
-        <v>2.4971</v>
+        <v>2.5381</v>
       </c>
       <c r="W7" t="n">
-        <v>3.6777</v>
+        <v>3.7283</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6349</v>
+        <v>-1.6422</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2657999999999998</v>
+        <v>0.3817000000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9006</v>
+        <v>-2.0238</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7907</v>
+        <v>0.8002</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1962</v>
+        <v>1.2241</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4055</v>
+        <v>-0.424</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5832</v>
+        <v>1.6463</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7785</v>
+        <v>0.8277</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8048000000000001</v>
+        <v>0.8186</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7925</v>
+        <v>-0.8461000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4177999999999999</v>
+        <v>0.3965</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2102</v>
+        <v>-1.2425</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R8" t="n">
-        <v>1.229</v>
+        <v>1.2148</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7383</v>
+        <v>0.7196</v>
       </c>
       <c r="T8" t="n">
-        <v>0.124</v>
+        <v>0.1365</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6143</v>
+        <v>0.5831000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.1639</v>
+        <v>-3.162</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.2124</v>
+        <v>-0.1865</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9515</v>
+        <v>-2.9755</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.118100000000001</v>
+        <v>-2.120200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9127000000000001</v>
+        <v>-0.79</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2053</v>
+        <v>-1.33</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6071</v>
+        <v>1.6147</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7638</v>
+        <v>-0.7706</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3709</v>
+        <v>2.3853</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9948</v>
+        <v>3.0584</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2374</v>
+        <v>-1.2261</v>
       </c>
       <c r="L9" t="n">
-        <v>4.232100000000001</v>
+        <v>4.2845</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3877</v>
+        <v>-1.4436</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4736</v>
+        <v>0.4556</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8612</v>
+        <v>-1.8992</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.229</v>
+        <v>-1.2148</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.277600000000001</v>
+        <v>-3.2392</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0484</v>
+        <v>2.0246</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8314</v>
+        <v>-0.8281000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6299</v>
+        <v>-0.6092</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2015</v>
+        <v>-0.2187999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3559</v>
+        <v>-3.4227</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.343</v>
+        <v>-4.1671</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9870999999999999</v>
+        <v>0.7444000000000002</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4009</v>
+        <v>-3.4562</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0469</v>
+        <v>-2.1118</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.354</v>
+        <v>-1.3444</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1625</v>
+        <v>-0.0751</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6303</v>
+        <v>0.6512</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7927</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2385</v>
+        <v>-3.3811</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6772</v>
+        <v>-2.763</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5612</v>
+        <v>-0.6181</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0484</v>
+        <v>-2.0246</v>
       </c>
       <c r="R10" t="n">
-        <v>4.3018</v>
+        <v>4.2515</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8153</v>
+        <v>-0.8168</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9811000000000001</v>
+        <v>-0.9417</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1657</v>
+        <v>0.1249</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3929</v>
+        <v>-1.3767</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.1509</v>
+        <v>-1.1257</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6616</v>
+        <v>-4.6355</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4895</v>
+        <v>-2.3177</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.172</v>
+        <v>-2.3177</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5633999999999999</v>
+        <v>0.5665</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.002399999999999958</v>
+        <v>0.01869999999999994</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5658000000000001</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7042</v>
+        <v>2.7991</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2526</v>
+        <v>1.3209</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4516</v>
+        <v>1.4782</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1408</v>
+        <v>-2.2325</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2551</v>
+        <v>-1.3022</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8858</v>
+        <v>-0.9303000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.3018</v>
+        <v>-4.2515</v>
       </c>
       <c r="R11" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1634</v>
+        <v>-2.1413</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8919</v>
+        <v>-0.8654000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2715</v>
+        <v>-1.2759</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>7.209999999999997</v>
+        <v>7.216799999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>16.1822</v>
+        <v>17.9309</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.9719</v>
+        <v>-10.7138</v>
       </c>
       <c r="G12" t="n">
-        <v>13.6174</v>
+        <v>13.6825</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5562999999999996</v>
+        <v>-0.4973000000000005</v>
       </c>
       <c r="I12" t="n">
-        <v>14.1739</v>
+        <v>14.1797</v>
       </c>
       <c r="J12" t="n">
-        <v>36.00129999999999</v>
+        <v>36.9957</v>
       </c>
       <c r="K12" t="n">
-        <v>10.8795</v>
+        <v>11.4365</v>
       </c>
       <c r="L12" t="n">
-        <v>25.1217</v>
+        <v>25.559</v>
       </c>
       <c r="M12" t="n">
-        <v>-22.3838</v>
+        <v>-23.3131</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.4359</v>
+        <v>-11.9336</v>
       </c>
       <c r="O12" t="n">
-        <v>-10.9477</v>
+        <v>-11.3792</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.048400000000001</v>
+        <v>-2.0246</v>
       </c>
       <c r="Q12" t="n">
-        <v>-32.7757</v>
+        <v>-32.3923</v>
       </c>
       <c r="R12" t="n">
-        <v>30.7269</v>
+        <v>30.3681</v>
       </c>
       <c r="S12" t="n">
-        <v>4.466200000000001</v>
+        <v>4.4207</v>
       </c>
       <c r="T12" t="n">
-        <v>5.058</v>
+        <v>5.239699999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5918000000000001</v>
+        <v>-0.8190000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-8.8248</v>
+        <v>-8.8621</v>
       </c>
       <c r="W12" t="n">
-        <v>7.899000000000001</v>
+        <v>8.087300000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-16.7239</v>
+        <v>-16.9493</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_COTO CÓRDOBA CB.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_COTO CÓRDOBA CB.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7206</v>
+        <v>6.5037</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9125</v>
+        <v>5.666700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8081</v>
+        <v>0.837</v>
       </c>
       <c r="G2" t="n">
         <v>3.6265</v>
@@ -610,13 +610,13 @@
         <v>4.6564</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3083</v>
+        <v>1.0914</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2852</v>
+        <v>1.0395</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02300000000000002</v>
+        <v>0.0519</v>
       </c>
       <c r="V2" t="n">
         <v>-0.846</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4206</v>
+        <v>5.6964</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0202</v>
+        <v>7.470700000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5996</v>
+        <v>-1.7744</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1381</v>
+        <v>7.9713</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4225</v>
+        <v>0.7106999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5606</v>
+        <v>7.2606</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4544</v>
+        <v>10.0202</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5798</v>
+        <v>3.0396</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8746</v>
+        <v>6.9806</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5925</v>
+        <v>-2.0489</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1572</v>
+        <v>-2.329</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.4352</v>
+        <v>0.2801</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2023999999999999</v>
+        <v>-0.2024000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2147</v>
+        <v>-4.049</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4172</v>
+        <v>3.8466</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1052</v>
+        <v>-0.7246</v>
       </c>
       <c r="T3" t="n">
-        <v>4.2787</v>
+        <v>-0.2857999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1735</v>
+        <v>-0.4388</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2509</v>
+        <v>-1.3479</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5018</v>
+        <v>1.7853</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2509</v>
+        <v>-3.1332</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.110799999999999</v>
+        <v>2.0615</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4325</v>
+        <v>3.3211</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3218</v>
+        <v>-1.2596</v>
       </c>
       <c r="G4" t="n">
-        <v>7.9713</v>
+        <v>-0.1381</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7106999999999999</v>
+        <v>1.4225</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2606</v>
+        <v>-1.5606</v>
       </c>
       <c r="J4" t="n">
-        <v>10.0202</v>
+        <v>2.4544</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0396</v>
+        <v>1.5798</v>
       </c>
       <c r="L4" t="n">
-        <v>6.9806</v>
+        <v>0.8746</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0489</v>
+        <v>-2.5925</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.329</v>
+        <v>-0.1572</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2801</v>
+        <v>-2.4352</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2024000000000001</v>
+        <v>0.2023999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.049</v>
+        <v>-1.2147</v>
       </c>
       <c r="R4" t="n">
-        <v>3.8466</v>
+        <v>1.4172</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.3102</v>
+        <v>1.7462</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3239</v>
+        <v>1.5795</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9862</v>
+        <v>0.1667</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.3479</v>
+        <v>0.2509</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7853</v>
+        <v>0.5018</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.1332</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1707</v>
+        <v>2.038</v>
       </c>
       <c r="E5" t="n">
-        <v>3.104</v>
+        <v>3.0001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9333</v>
+        <v>-0.9621</v>
       </c>
       <c r="G5" t="n">
         <v>2.1032</v>
@@ -844,13 +844,13 @@
         <v>3.4417</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2698</v>
+        <v>1.1373</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9444</v>
+        <v>0.8406</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3253999999999999</v>
+        <v>0.2967</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5951000000000002</v>
@@ -877,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0438</v>
+        <v>1.646</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2117</v>
+        <v>1.9003</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1679</v>
+        <v>-0.2543</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3524</v>
@@ -922,13 +922,13 @@
         <v>4.2515</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3718</v>
+        <v>1.9739</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5084</v>
+        <v>1.1969</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8633</v>
+        <v>0.7768999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1902</v>
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4291</v>
+        <v>-0.4314</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1431</v>
+        <v>0.9736000000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5722</v>
+        <v>-1.405</v>
       </c>
       <c r="G7" t="n">
         <v>0.9467999999999996</v>
@@ -1000,13 +1000,13 @@
         <v>2.6319</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2575999999999999</v>
+        <v>0.7402</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1733</v>
+        <v>0.6572</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0843</v>
+        <v>0.0829</v>
       </c>
       <c r="V7" t="n">
         <v>2.5381</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>D. ROLLINS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6422</v>
+        <v>-1.3241</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3817000000000002</v>
+        <v>0.04039999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0238</v>
+        <v>-1.3645</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8002</v>
+        <v>1.6147</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2241</v>
+        <v>-0.7706</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.424</v>
+        <v>2.3853</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6463</v>
+        <v>3.0584</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8277</v>
+        <v>-1.2261</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8186</v>
+        <v>4.2845</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8461000000000001</v>
+        <v>-1.4436</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3965</v>
+        <v>0.4556</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2425</v>
+        <v>-1.8992</v>
       </c>
       <c r="P8" t="n">
+        <v>-1.2148</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-3.2392</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.0246</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.03199999999999997</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.2212</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.2533</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-1.6921</v>
+      </c>
+      <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.2147</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.2148</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.7196</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.1365</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.5831000000000001</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-3.162</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.1865</v>
-      </c>
       <c r="X8" t="n">
-        <v>-2.9755</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. ROLLINS</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.120200000000001</v>
+        <v>-1.538</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.79</v>
+        <v>0.6931</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.33</v>
+        <v>-2.2312</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6147</v>
+        <v>0.8002</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7706</v>
+        <v>1.2241</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3853</v>
+        <v>-0.424</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0584</v>
+        <v>1.6463</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2261</v>
+        <v>0.8277</v>
       </c>
       <c r="L9" t="n">
-        <v>4.2845</v>
+        <v>0.8186</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4436</v>
+        <v>-0.8461000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4556</v>
+        <v>0.3965</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8992</v>
+        <v>-1.2425</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2148</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.2392</v>
+        <v>-1.2147</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0246</v>
+        <v>1.2148</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8281000000000001</v>
+        <v>0.8236999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6092</v>
+        <v>0.448</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2187999999999999</v>
+        <v>0.3758</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6921</v>
+        <v>-3.162</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.1865</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6921</v>
+        <v>-2.9755</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4227</v>
+        <v>-2.8053</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1671</v>
+        <v>-3.2327</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7444000000000002</v>
+        <v>0.4274</v>
       </c>
       <c r="G10" t="n">
         <v>-3.4562</v>
@@ -1234,13 +1234,13 @@
         <v>4.2515</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8168</v>
+        <v>-0.1994</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9417</v>
+        <v>-0.0073</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1249</v>
+        <v>-0.1920999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3767</v>
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6355</v>
+        <v>-3.9377</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3177</v>
+        <v>-1.9025</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3177</v>
+        <v>-2.0352</v>
       </c>
       <c r="G11" t="n">
         <v>0.5665</v>
@@ -1312,13 +1312,13 @@
         <v>2.6319</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1413</v>
+        <v>-1.4435</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8654000000000001</v>
+        <v>-0.4502</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2759</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4411</v>
@@ -1345,19 +1345,19 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>7.216799999999999</v>
+        <v>7.909099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>17.9309</v>
+        <v>17.9308</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.7138</v>
+        <v>-10.0219</v>
       </c>
       <c r="G12" t="n">
         <v>13.6825</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4973000000000005</v>
+        <v>-0.4972999999999996</v>
       </c>
       <c r="I12" t="n">
         <v>14.1797</v>
@@ -1390,13 +1390,13 @@
         <v>30.3681</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4207</v>
+        <v>5.1132</v>
       </c>
       <c r="T12" t="n">
-        <v>5.239699999999999</v>
+        <v>5.239599999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8190000000000001</v>
+        <v>-0.1266999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-8.8621</v>
